--- a/Output Excel/lfsa_egan22d_final.xlsx
+++ b/Output Excel/lfsa_egan22d_final.xlsx
@@ -6771,7 +6771,7 @@
         <v>2025</v>
       </c>
       <c r="B148" t="n">
-        <v>1361.6</v>
+        <v>1361.7</v>
       </c>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
@@ -20749,7 +20749,7 @@
         <v>2025</v>
       </c>
       <c r="B475" t="n">
-        <v>159703.4</v>
+        <v>159703.5</v>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
@@ -22629,7 +22629,7 @@
         <v>2025</v>
       </c>
       <c r="B519" t="n">
-        <v>201627.4</v>
+        <v>201627.5</v>
       </c>
       <c r="C519" t="inlineStr"/>
       <c r="D519" t="inlineStr">
@@ -26859,7 +26859,7 @@
         <v>2025</v>
       </c>
       <c r="B618" t="n">
-        <v>323</v>
+        <v>323.1</v>
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr">
